--- a/dados/orcamentos_tematicos/crianca_adolescente/OCA_QUADRIMESTRE/2017/Relatório do Orçamento Criança e Adolescente 2017_0.xlsx
+++ b/dados/orcamentos_tematicos/crianca_adolescente/OCA_QUADRIMESTRE/2017/Relatório do Orçamento Criança e Adolescente 2017_0.xlsx
@@ -1,20 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PASTA CIDA\PPAG\Doc 2018\Publicação no site\Relatórios 2017\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\Documents\pbh_visualizacao_de_dados\dados\orcamentos_tematicos\crianca_adolescente\OCA_QUADRIMESTRE\2017\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80A973D9-82E1-4ED8-AF3F-545B6FDBB5F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Relatório do Orçamento Criança " sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1686,8 +1701,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1706,6 +1721,23 @@
     <font>
       <b/>
       <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1747,7 +1779,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -1764,7 +1796,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2044,35 +2077,35 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T389"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" style="3" customWidth="1"/>
     <col min="3" max="3" width="5" style="3" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="5.42578125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="4.5703125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="6.5703125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" style="3" customWidth="1"/>
-    <col min="10" max="10" width="5.85546875" style="3" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" style="3" customWidth="1"/>
-    <col min="12" max="12" width="6.7109375" style="3" customWidth="1"/>
-    <col min="13" max="13" width="12.7109375" style="3" customWidth="1"/>
-    <col min="14" max="14" width="6.5703125" style="3" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" style="3" customWidth="1"/>
-    <col min="16" max="16" width="6.28515625" style="3" customWidth="1"/>
-    <col min="17" max="17" width="16.42578125" style="3" customWidth="1"/>
-    <col min="18" max="18" width="16.5703125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="5.44140625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="4.5546875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="9.5546875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="6.5546875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="5.88671875" style="3" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="6.6640625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="12.6640625" style="3" customWidth="1"/>
+    <col min="14" max="14" width="6.5546875" style="3" customWidth="1"/>
+    <col min="15" max="15" width="12.6640625" style="3" customWidth="1"/>
+    <col min="16" max="16" width="6.33203125" style="3" customWidth="1"/>
+    <col min="17" max="17" width="16.44140625" style="3" customWidth="1"/>
+    <col min="18" max="18" width="16.5546875" style="3" customWidth="1"/>
     <col min="19" max="19" width="16" style="3" customWidth="1"/>
-    <col min="20" max="20" width="16.140625" style="3" customWidth="1"/>
-    <col min="21" max="256" width="12.7109375" style="3" customWidth="1"/>
-    <col min="257" max="16384" width="9.140625" style="3"/>
+    <col min="20" max="20" width="16.109375" style="3" customWidth="1"/>
+    <col min="21" max="256" width="12.6640625" style="3" customWidth="1"/>
+    <col min="257" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="6" t="s">
         <v>553</v>
       </c>
@@ -2096,7 +2129,7 @@
       <c r="S1" s="6"/>
       <c r="T1" s="6"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>542</v>
       </c>
@@ -2158,7 +2191,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -2220,7 +2253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -2282,7 +2315,7 @@
         <v>28011.72</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
@@ -2344,7 +2377,7 @@
         <v>973.01250000000005</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
@@ -2406,7 +2439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>5</v>
       </c>
@@ -2468,7 +2501,7 @@
         <v>2236285.2450000001</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>5</v>
       </c>
@@ -2530,7 +2563,7 @@
         <v>5665.33</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>5</v>
       </c>
@@ -2592,7 +2625,7 @@
         <v>51305.595000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>5</v>
       </c>
@@ -2654,7 +2687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>5</v>
       </c>
@@ -2716,7 +2749,7 @@
         <v>1546783.0375000001</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>5</v>
       </c>
@@ -2778,7 +2811,7 @@
         <v>2679299.9624999999</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>5</v>
       </c>
@@ -2840,7 +2873,7 @@
         <v>1505095.1924999999</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>5</v>
       </c>
@@ -2902,7 +2935,7 @@
         <v>7535.25</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>5</v>
       </c>
@@ -2964,7 +2997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>5</v>
       </c>
@@ -3026,7 +3059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>5</v>
       </c>
@@ -3088,7 +3121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>5</v>
       </c>
@@ -3150,7 +3183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>5</v>
       </c>
@@ -3212,7 +3245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>5</v>
       </c>
@@ -3274,7 +3307,7 @@
         <v>381127.03749999998</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>5</v>
       </c>
@@ -3336,7 +3369,7 @@
         <v>1458786.4375</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>5</v>
       </c>
@@ -3398,7 +3431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>5</v>
       </c>
@@ -3460,7 +3493,7 @@
         <v>297765.31900000002</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>5</v>
       </c>
@@ -3522,7 +3555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>5</v>
       </c>
@@ -3584,7 +3617,7 @@
         <v>90875.4375</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>5</v>
       </c>
@@ -3646,7 +3679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>5</v>
       </c>
@@ -3708,7 +3741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>5</v>
       </c>
@@ -3770,7 +3803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>5</v>
       </c>
@@ -3832,7 +3865,7 @@
         <v>57933.767500000002</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>5</v>
       </c>
@@ -3894,7 +3927,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>5</v>
       </c>
@@ -3956,7 +3989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>5</v>
       </c>
@@ -4018,7 +4051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>5</v>
       </c>
@@ -4080,7 +4113,7 @@
         <v>207748.185</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>5</v>
       </c>
@@ -4142,7 +4175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>5</v>
       </c>
@@ -4204,7 +4237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>5</v>
       </c>
@@ -4266,7 +4299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>5</v>
       </c>
@@ -4328,7 +4361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>5</v>
       </c>
@@ -4390,7 +4423,7 @@
         <v>49877.25</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>5</v>
       </c>
@@ -4452,7 +4485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>5</v>
       </c>
@@ -4514,7 +4547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>5</v>
       </c>
@@ -4576,7 +4609,7 @@
         <v>112000</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>5</v>
       </c>
@@ -4638,7 +4671,7 @@
         <v>1323549.2024999999</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>5</v>
       </c>
@@ -4700,7 +4733,7 @@
         <v>912.5</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>5</v>
       </c>
@@ -4762,7 +4795,7 @@
         <v>694919.07</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>5</v>
       </c>
@@ -4824,7 +4857,7 @@
         <v>204380</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>5</v>
       </c>
@@ -4886,7 +4919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>5</v>
       </c>
@@ -4948,7 +4981,7 @@
         <v>979024.54249999998</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>5</v>
       </c>
@@ -5010,7 +5043,7 @@
         <v>262254.60499999998</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>5</v>
       </c>
@@ -5072,7 +5105,7 @@
         <v>2044022.7849999999</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>5</v>
       </c>
@@ -5134,7 +5167,7 @@
         <v>46255.447500000002</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>5</v>
       </c>
@@ -5196,7 +5229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>5</v>
       </c>
@@ -5258,7 +5291,7 @@
         <v>165799</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>5</v>
       </c>
@@ -5320,7 +5353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>5</v>
       </c>
@@ -5382,7 +5415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>5</v>
       </c>
@@ -5444,7 +5477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>5</v>
       </c>
@@ -5506,7 +5539,7 @@
         <v>44106.49</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>5</v>
       </c>
@@ -5568,7 +5601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>5</v>
       </c>
@@ -5630,7 +5663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>5</v>
       </c>
@@ -5692,7 +5725,7 @@
         <v>1940568.9040000001</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>5</v>
       </c>
@@ -5754,7 +5787,7 @@
         <v>16495.73</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>5</v>
       </c>
@@ -5816,7 +5849,7 @@
         <v>16293.13</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>5</v>
       </c>
@@ -5878,7 +5911,7 @@
         <v>8160</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>5</v>
       </c>
@@ -5940,7 +5973,7 @@
         <v>24890</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
         <v>5</v>
       </c>
@@ -6002,7 +6035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>5</v>
       </c>
@@ -6064,7 +6097,7 @@
         <v>6409726.7000000002</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>5</v>
       </c>
@@ -6126,7 +6159,7 @@
         <v>6347784.3600000003</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
         <v>5</v>
       </c>
@@ -6188,7 +6221,7 @@
         <v>8151044.2000000002</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
         <v>5</v>
       </c>
@@ -6250,7 +6283,7 @@
         <v>702280.35</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
         <v>5</v>
       </c>
@@ -6312,7 +6345,7 @@
         <v>7312300.0800000001</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
         <v>5</v>
       </c>
@@ -6374,7 +6407,7 @@
         <v>2640886.5099999998</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>5</v>
       </c>
@@ -6436,7 +6469,7 @@
         <v>26313.730500000001</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
         <v>5</v>
       </c>
@@ -6498,7 +6531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
         <v>5</v>
       </c>
@@ -6560,7 +6593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
         <v>5</v>
       </c>
@@ -6622,7 +6655,7 @@
         <v>46151.6</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
         <v>5</v>
       </c>
@@ -6684,7 +6717,7 @@
         <v>71185496.650000006</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
         <v>5</v>
       </c>
@@ -6746,7 +6779,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
         <v>5</v>
       </c>
@@ -6808,7 +6841,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
         <v>5</v>
       </c>
@@ -6870,7 +6903,7 @@
         <v>247002.59</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
         <v>5</v>
       </c>
@@ -6932,7 +6965,7 @@
         <v>513909.54</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
         <v>5</v>
       </c>
@@ -6994,7 +7027,7 @@
         <v>635877.67000000004</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
         <v>5</v>
       </c>
@@ -7056,7 +7089,7 @@
         <v>13291960.66</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
         <v>5</v>
       </c>
@@ -7118,7 +7151,7 @@
         <v>28313550.300000001</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
         <v>5</v>
       </c>
@@ -7180,7 +7213,7 @@
         <v>1551784.03</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
         <v>5</v>
       </c>
@@ -7242,7 +7275,7 @@
         <v>9378147.7699999996</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
         <v>5</v>
       </c>
@@ -7304,7 +7337,7 @@
         <v>205885224</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
         <v>5</v>
       </c>
@@ -7366,7 +7399,7 @@
         <v>540000</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
         <v>5</v>
       </c>
@@ -7428,7 +7461,7 @@
         <v>617782128.38999999</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
         <v>5</v>
       </c>
@@ -7490,7 +7523,7 @@
         <v>3916785.57</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
         <v>5</v>
       </c>
@@ -7552,7 +7585,7 @@
         <v>2184423.17</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
         <v>5</v>
       </c>
@@ -7614,7 +7647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>5</v>
       </c>
@@ -7676,7 +7709,7 @@
         <v>7786866.6799999997</v>
       </c>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>5</v>
       </c>
@@ -7738,7 +7771,7 @@
         <v>4024393.55</v>
       </c>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>5</v>
       </c>
@@ -7800,7 +7833,7 @@
         <v>248853.01</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>5</v>
       </c>
@@ -7862,7 +7895,7 @@
         <v>10624189.35</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
         <v>5</v>
       </c>
@@ -7924,7 +7957,7 @@
         <v>13256067.050000001</v>
       </c>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
         <v>5</v>
       </c>
@@ -7986,7 +8019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
         <v>5</v>
       </c>
@@ -8048,7 +8081,7 @@
         <v>25281577</v>
       </c>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
         <v>5</v>
       </c>
@@ -8110,7 +8143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
         <v>5</v>
       </c>
@@ -8172,7 +8205,7 @@
         <v>5082997.24</v>
       </c>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
         <v>5</v>
       </c>
@@ -8234,7 +8267,7 @@
         <v>9863639</v>
       </c>
     </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>5</v>
       </c>
@@ -8296,7 +8329,7 @@
         <v>886250</v>
       </c>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
         <v>5</v>
       </c>
@@ -8358,7 +8391,7 @@
         <v>9762505.4800000004</v>
       </c>
     </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
         <v>5</v>
       </c>
@@ -8420,7 +8453,7 @@
         <v>2563850.7400000002</v>
       </c>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
         <v>5</v>
       </c>
@@ -8482,7 +8515,7 @@
         <v>3058120.5</v>
       </c>
     </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
         <v>5</v>
       </c>
@@ -8544,7 +8577,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
         <v>5</v>
       </c>
@@ -8606,7 +8639,7 @@
         <v>6327</v>
       </c>
     </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
         <v>5</v>
       </c>
@@ -8668,7 +8701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
         <v>5</v>
       </c>
@@ -8730,7 +8763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
         <v>5</v>
       </c>
@@ -8792,7 +8825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
         <v>5</v>
       </c>
@@ -8854,7 +8887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
         <v>5</v>
       </c>
@@ -8916,7 +8949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
         <v>5</v>
       </c>
@@ -8978,7 +9011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
         <v>5</v>
       </c>
@@ -9040,7 +9073,7 @@
         <v>3226900.35</v>
       </c>
     </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
         <v>5</v>
       </c>
@@ -9102,7 +9135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
         <v>5</v>
       </c>
@@ -9164,7 +9197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
         <v>5</v>
       </c>
@@ -9226,7 +9259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
         <v>5</v>
       </c>
@@ -9288,7 +9321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
         <v>5</v>
       </c>
@@ -9350,7 +9383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
         <v>5</v>
       </c>
@@ -9412,7 +9445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
         <v>5</v>
       </c>
@@ -9474,7 +9507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
         <v>5</v>
       </c>
@@ -9536,7 +9569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A122" s="4" t="s">
         <v>5</v>
       </c>
@@ -9598,7 +9631,7 @@
         <v>26407173.800000001</v>
       </c>
     </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
         <v>5</v>
       </c>
@@ -9660,7 +9693,7 @@
         <v>1693787.73</v>
       </c>
     </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A124" s="4" t="s">
         <v>5</v>
       </c>
@@ -9722,7 +9755,7 @@
         <v>1557820</v>
       </c>
     </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A125" s="4" t="s">
         <v>5</v>
       </c>
@@ -9784,7 +9817,7 @@
         <v>29604604</v>
       </c>
     </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A126" s="4" t="s">
         <v>5</v>
       </c>
@@ -9846,7 +9879,7 @@
         <v>241451997.22</v>
       </c>
     </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A127" s="4" t="s">
         <v>5</v>
       </c>
@@ -9908,7 +9941,7 @@
         <v>4236051.82</v>
       </c>
     </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A128" s="4" t="s">
         <v>5</v>
       </c>
@@ -9970,7 +10003,7 @@
         <v>1385602.11</v>
       </c>
     </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A129" s="4" t="s">
         <v>5</v>
       </c>
@@ -10032,7 +10065,7 @@
         <v>101913220</v>
       </c>
     </row>
-    <row r="130" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A130" s="4" t="s">
         <v>5</v>
       </c>
@@ -10094,7 +10127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A131" s="4" t="s">
         <v>5</v>
       </c>
@@ -10156,7 +10189,7 @@
         <v>47551580.920000002</v>
       </c>
     </row>
-    <row r="132" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A132" s="4" t="s">
         <v>5</v>
       </c>
@@ -10218,7 +10251,7 @@
         <v>81939.58</v>
       </c>
     </row>
-    <row r="133" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A133" s="4" t="s">
         <v>5</v>
       </c>
@@ -10280,7 +10313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A134" s="4" t="s">
         <v>5</v>
       </c>
@@ -10342,7 +10375,7 @@
         <v>1512261.4</v>
       </c>
     </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A135" s="4" t="s">
         <v>5</v>
       </c>
@@ -10404,7 +10437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A136" s="4" t="s">
         <v>5</v>
       </c>
@@ -10466,7 +10499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A137" s="4" t="s">
         <v>5</v>
       </c>
@@ -10528,7 +10561,7 @@
         <v>1254848.5</v>
       </c>
     </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A138" s="4" t="s">
         <v>5</v>
       </c>
@@ -10590,7 +10623,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A139" s="4" t="s">
         <v>5</v>
       </c>
@@ -10652,7 +10685,7 @@
         <v>22862122.260000002</v>
       </c>
     </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A140" s="4" t="s">
         <v>5</v>
       </c>
@@ -10714,7 +10747,7 @@
         <v>144588.9</v>
       </c>
     </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A141" s="4" t="s">
         <v>5</v>
       </c>
@@ -10776,7 +10809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A142" s="4" t="s">
         <v>5</v>
       </c>
@@ -10838,7 +10871,7 @@
         <v>309000</v>
       </c>
     </row>
-    <row r="143" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A143" s="4" t="s">
         <v>5</v>
       </c>
@@ -10900,7 +10933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A144" s="4" t="s">
         <v>5</v>
       </c>
@@ -10962,7 +10995,7 @@
         <v>1882862.81</v>
       </c>
     </row>
-    <row r="145" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A145" s="4" t="s">
         <v>5</v>
       </c>
@@ -11024,7 +11057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A146" s="4" t="s">
         <v>5</v>
       </c>
@@ -11086,7 +11119,7 @@
         <v>5343081.99</v>
       </c>
     </row>
-    <row r="147" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A147" s="4" t="s">
         <v>5</v>
       </c>
@@ -11148,7 +11181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A148" s="4" t="s">
         <v>5</v>
       </c>
@@ -11210,7 +11243,7 @@
         <v>3315614.5350000001</v>
       </c>
     </row>
-    <row r="149" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A149" s="4" t="s">
         <v>5</v>
       </c>
@@ -11272,7 +11305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A150" s="4" t="s">
         <v>5</v>
       </c>
@@ -11334,7 +11367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A151" s="4" t="s">
         <v>5</v>
       </c>
@@ -11396,7 +11429,7 @@
         <v>25975.522499999999</v>
       </c>
     </row>
-    <row r="152" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A152" s="4" t="s">
         <v>5</v>
       </c>
@@ -11458,7 +11491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A153" s="4" t="s">
         <v>5</v>
       </c>
@@ -11520,7 +11553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A154" s="4" t="s">
         <v>5</v>
       </c>
@@ -11582,7 +11615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A155" s="4" t="s">
         <v>5</v>
       </c>
@@ -11644,7 +11677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A156" s="4" t="s">
         <v>5</v>
       </c>
@@ -11706,7 +11739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A157" s="4" t="s">
         <v>5</v>
       </c>
@@ -11768,7 +11801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A158" s="4" t="s">
         <v>5</v>
       </c>
@@ -11830,7 +11863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A159" s="4" t="s">
         <v>235</v>
       </c>
@@ -11892,7 +11925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A160" s="4" t="s">
         <v>235</v>
       </c>
@@ -11954,7 +11987,7 @@
         <v>55667.105000000003</v>
       </c>
     </row>
-    <row r="161" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A161" s="4" t="s">
         <v>235</v>
       </c>
@@ -12016,7 +12049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A162" s="4" t="s">
         <v>235</v>
       </c>
@@ -12078,7 +12111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A163" s="4" t="s">
         <v>235</v>
       </c>
@@ -12140,7 +12173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A164" s="4" t="s">
         <v>235</v>
       </c>
@@ -12202,7 +12235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A165" s="4" t="s">
         <v>235</v>
       </c>
@@ -12264,7 +12297,7 @@
         <v>1615156.46</v>
       </c>
     </row>
-    <row r="166" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A166" s="4" t="s">
         <v>235</v>
       </c>
@@ -12326,7 +12359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A167" s="4" t="s">
         <v>235</v>
       </c>
@@ -12388,7 +12421,7 @@
         <v>258721.98</v>
       </c>
     </row>
-    <row r="168" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A168" s="4" t="s">
         <v>235</v>
       </c>
@@ -12450,7 +12483,7 @@
         <v>191291.33</v>
       </c>
     </row>
-    <row r="169" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A169" s="4" t="s">
         <v>235</v>
       </c>
@@ -12512,7 +12545,7 @@
         <v>448433</v>
       </c>
     </row>
-    <row r="170" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A170" s="4" t="s">
         <v>235</v>
       </c>
@@ -12574,7 +12607,7 @@
         <v>1685944.6</v>
       </c>
     </row>
-    <row r="171" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A171" s="4" t="s">
         <v>235</v>
       </c>
@@ -12636,7 +12669,7 @@
         <v>20827112.489999998</v>
       </c>
     </row>
-    <row r="172" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A172" s="4" t="s">
         <v>235</v>
       </c>
@@ -12698,7 +12731,7 @@
         <v>605423.04</v>
       </c>
     </row>
-    <row r="173" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A173" s="4" t="s">
         <v>235</v>
       </c>
@@ -12760,7 +12793,7 @@
         <v>3237977.45</v>
       </c>
     </row>
-    <row r="174" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A174" s="4" t="s">
         <v>235</v>
       </c>
@@ -12822,7 +12855,7 @@
         <v>490034.31</v>
       </c>
     </row>
-    <row r="175" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A175" s="4" t="s">
         <v>235</v>
       </c>
@@ -12884,7 +12917,7 @@
         <v>1600015.66</v>
       </c>
     </row>
-    <row r="176" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A176" s="4" t="s">
         <v>235</v>
       </c>
@@ -12946,7 +12979,7 @@
         <v>541737.16</v>
       </c>
     </row>
-    <row r="177" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A177" s="4" t="s">
         <v>235</v>
       </c>
@@ -13008,7 +13041,7 @@
         <v>672602.98</v>
       </c>
     </row>
-    <row r="178" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A178" s="4" t="s">
         <v>235</v>
       </c>
@@ -13070,7 +13103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A179" s="4" t="s">
         <v>235</v>
       </c>
@@ -13132,7 +13165,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="180" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A180" s="4" t="s">
         <v>235</v>
       </c>
@@ -13194,7 +13227,7 @@
         <v>12790.55</v>
       </c>
     </row>
-    <row r="181" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A181" s="4" t="s">
         <v>235</v>
       </c>
@@ -13256,7 +13289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A182" s="4" t="s">
         <v>235</v>
       </c>
@@ -13318,7 +13351,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="183" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A183" s="4" t="s">
         <v>235</v>
       </c>
@@ -13380,7 +13413,7 @@
         <v>1071.18</v>
       </c>
     </row>
-    <row r="184" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A184" s="4" t="s">
         <v>235</v>
       </c>
@@ -13442,7 +13475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A185" s="4" t="s">
         <v>235</v>
       </c>
@@ -13504,7 +13537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A186" s="4" t="s">
         <v>235</v>
       </c>
@@ -13566,7 +13599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A187" s="4" t="s">
         <v>235</v>
       </c>
@@ -13628,7 +13661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A188" s="4" t="s">
         <v>235</v>
       </c>
@@ -13690,7 +13723,7 @@
         <v>1845366</v>
       </c>
     </row>
-    <row r="189" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A189" s="4" t="s">
         <v>235</v>
       </c>
@@ -13752,7 +13785,7 @@
         <v>23164182.73</v>
       </c>
     </row>
-    <row r="190" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A190" s="4" t="s">
         <v>235</v>
       </c>
@@ -13814,7 +13847,7 @@
         <v>633123.94999999995</v>
       </c>
     </row>
-    <row r="191" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A191" s="4" t="s">
         <v>235</v>
       </c>
@@ -13876,7 +13909,7 @@
         <v>1053633.47</v>
       </c>
     </row>
-    <row r="192" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A192" s="4" t="s">
         <v>235</v>
       </c>
@@ -13938,7 +13971,7 @@
         <v>322934.80249999999</v>
       </c>
     </row>
-    <row r="193" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A193" s="4" t="s">
         <v>235</v>
       </c>
@@ -14000,7 +14033,7 @@
         <v>557792.33750000002</v>
       </c>
     </row>
-    <row r="194" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A194" s="4" t="s">
         <v>235</v>
       </c>
@@ -14062,7 +14095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A195" s="4" t="s">
         <v>235</v>
       </c>
@@ -14124,7 +14157,7 @@
         <v>90000</v>
       </c>
     </row>
-    <row r="196" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A196" s="4" t="s">
         <v>235</v>
       </c>
@@ -14186,7 +14219,7 @@
         <v>415186.22749999998</v>
       </c>
     </row>
-    <row r="197" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A197" s="4" t="s">
         <v>235</v>
       </c>
@@ -14248,7 +14281,7 @@
         <v>320508.79999999999</v>
       </c>
     </row>
-    <row r="198" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A198" s="4" t="s">
         <v>235</v>
       </c>
@@ -14310,7 +14343,7 @@
         <v>453544.14250000002</v>
       </c>
     </row>
-    <row r="199" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A199" s="4" t="s">
         <v>235</v>
       </c>
@@ -14372,7 +14405,7 @@
         <v>828490.98</v>
       </c>
     </row>
-    <row r="200" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A200" s="4" t="s">
         <v>235</v>
       </c>
@@ -14434,7 +14467,7 @@
         <v>74904.994999999995</v>
       </c>
     </row>
-    <row r="201" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A201" s="4" t="s">
         <v>235</v>
       </c>
@@ -14496,7 +14529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A202" s="4" t="s">
         <v>235</v>
       </c>
@@ -14558,7 +14591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A203" s="4" t="s">
         <v>235</v>
       </c>
@@ -14620,7 +14653,7 @@
         <v>417900</v>
       </c>
     </row>
-    <row r="204" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A204" s="4" t="s">
         <v>235</v>
       </c>
@@ -14682,7 +14715,7 @@
         <v>8146224.5650000004</v>
       </c>
     </row>
-    <row r="205" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A205" s="4" t="s">
         <v>235</v>
       </c>
@@ -14744,7 +14777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A206" s="4" t="s">
         <v>235</v>
       </c>
@@ -14806,7 +14839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A207" s="4" t="s">
         <v>235</v>
       </c>
@@ -14868,7 +14901,7 @@
         <v>1015.6</v>
       </c>
     </row>
-    <row r="208" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A208" s="4" t="s">
         <v>235</v>
       </c>
@@ -14930,7 +14963,7 @@
         <v>40100</v>
       </c>
     </row>
-    <row r="209" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A209" s="4" t="s">
         <v>235</v>
       </c>
@@ -14992,7 +15025,7 @@
         <v>783801.14500000002</v>
       </c>
     </row>
-    <row r="210" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A210" s="4" t="s">
         <v>235</v>
       </c>
@@ -15054,7 +15087,7 @@
         <v>16255.9175</v>
       </c>
     </row>
-    <row r="211" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A211" s="4" t="s">
         <v>235</v>
       </c>
@@ -15116,7 +15149,7 @@
         <v>114178.69749999999</v>
       </c>
     </row>
-    <row r="212" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A212" s="4" t="s">
         <v>235</v>
       </c>
@@ -15178,7 +15211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A213" s="4" t="s">
         <v>235</v>
       </c>
@@ -15240,7 +15273,7 @@
         <v>1813.4849999999999</v>
       </c>
     </row>
-    <row r="214" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A214" s="4" t="s">
         <v>235</v>
       </c>
@@ -15302,7 +15335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A215" s="4" t="s">
         <v>235</v>
       </c>
@@ -15364,7 +15397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A216" s="4" t="s">
         <v>235</v>
       </c>
@@ -15426,7 +15459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A217" s="4" t="s">
         <v>235</v>
       </c>
@@ -15488,7 +15521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A218" s="4" t="s">
         <v>235</v>
       </c>
@@ -15550,7 +15583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A219" s="4" t="s">
         <v>235</v>
       </c>
@@ -15612,7 +15645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A220" s="4" t="s">
         <v>235</v>
       </c>
@@ -15674,7 +15707,7 @@
         <v>4947.5024999999996</v>
       </c>
     </row>
-    <row r="221" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A221" s="4" t="s">
         <v>235</v>
       </c>
@@ -15736,7 +15769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A222" s="4" t="s">
         <v>235</v>
       </c>
@@ -15798,7 +15831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A223" s="4" t="s">
         <v>235</v>
       </c>
@@ -15860,7 +15893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A224" s="4" t="s">
         <v>235</v>
       </c>
@@ -15922,7 +15955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A225" s="4" t="s">
         <v>235</v>
       </c>
@@ -15984,7 +16017,7 @@
         <v>2610529.5575000001</v>
       </c>
     </row>
-    <row r="226" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A226" s="4" t="s">
         <v>235</v>
       </c>
@@ -16046,7 +16079,7 @@
         <v>552855.17000000004</v>
       </c>
     </row>
-    <row r="227" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A227" s="4" t="s">
         <v>235</v>
       </c>
@@ -16108,7 +16141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A228" s="4" t="s">
         <v>235</v>
       </c>
@@ -16170,7 +16203,7 @@
         <v>2224352.4550000001</v>
       </c>
     </row>
-    <row r="229" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A229" s="4" t="s">
         <v>235</v>
       </c>
@@ -16232,7 +16265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A230" s="4" t="s">
         <v>235</v>
       </c>
@@ -16294,7 +16327,7 @@
         <v>61486.667500000003</v>
       </c>
     </row>
-    <row r="231" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A231" s="4" t="s">
         <v>235</v>
       </c>
@@ -16356,7 +16389,7 @@
         <v>613974.11750000005</v>
       </c>
     </row>
-    <row r="232" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A232" s="4" t="s">
         <v>235</v>
       </c>
@@ -16418,7 +16451,7 @@
         <v>214863.8</v>
       </c>
     </row>
-    <row r="233" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A233" s="4" t="s">
         <v>235</v>
       </c>
@@ -16480,7 +16513,7 @@
         <v>383522.07250000001</v>
       </c>
     </row>
-    <row r="234" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A234" s="4" t="s">
         <v>235</v>
       </c>
@@ -16542,7 +16575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A235" s="4" t="s">
         <v>235</v>
       </c>
@@ -16604,7 +16637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A236" s="4" t="s">
         <v>235</v>
       </c>
@@ -16666,7 +16699,7 @@
         <v>1027983.85</v>
       </c>
     </row>
-    <row r="237" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A237" s="4" t="s">
         <v>235</v>
       </c>
@@ -16728,7 +16761,7 @@
         <v>2023.357</v>
       </c>
     </row>
-    <row r="238" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A238" s="4" t="s">
         <v>235</v>
       </c>
@@ -16790,7 +16823,7 @@
         <v>2964814.62</v>
       </c>
     </row>
-    <row r="239" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A239" s="4" t="s">
         <v>235</v>
       </c>
@@ -16852,7 +16885,7 @@
         <v>85861.93</v>
       </c>
     </row>
-    <row r="240" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A240" s="4" t="s">
         <v>235</v>
       </c>
@@ -16914,7 +16947,7 @@
         <v>111660</v>
       </c>
     </row>
-    <row r="241" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A241" s="4" t="s">
         <v>235</v>
       </c>
@@ -16976,7 +17009,7 @@
         <v>266518.755</v>
       </c>
     </row>
-    <row r="242" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A242" s="4" t="s">
         <v>235</v>
       </c>
@@ -17038,7 +17071,7 @@
         <v>48156.52</v>
       </c>
     </row>
-    <row r="243" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A243" s="4" t="s">
         <v>235</v>
       </c>
@@ -17100,7 +17133,7 @@
         <v>249390.76</v>
       </c>
     </row>
-    <row r="244" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A244" s="4" t="s">
         <v>235</v>
       </c>
@@ -17162,7 +17195,7 @@
         <v>263425.897</v>
       </c>
     </row>
-    <row r="245" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A245" s="4" t="s">
         <v>235</v>
       </c>
@@ -17224,7 +17257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A246" s="4" t="s">
         <v>235</v>
       </c>
@@ -17286,7 +17319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A247" s="4" t="s">
         <v>235</v>
       </c>
@@ -17348,7 +17381,7 @@
         <v>2410860.6274999999</v>
       </c>
     </row>
-    <row r="248" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A248" s="4" t="s">
         <v>235</v>
       </c>
@@ -17410,7 +17443,7 @@
         <v>6097458.3375000004</v>
       </c>
     </row>
-    <row r="249" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A249" s="4" t="s">
         <v>235</v>
       </c>
@@ -17472,7 +17505,7 @@
         <v>7237465.0449999999</v>
       </c>
     </row>
-    <row r="250" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A250" s="4" t="s">
         <v>235</v>
       </c>
@@ -17534,7 +17567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A251" s="4" t="s">
         <v>235</v>
       </c>
@@ -17596,7 +17629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A252" s="4" t="s">
         <v>235</v>
       </c>
@@ -17658,7 +17691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A253" s="4" t="s">
         <v>235</v>
       </c>
@@ -17720,7 +17753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A254" s="4" t="s">
         <v>235</v>
       </c>
@@ -17782,7 +17815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A255" s="4" t="s">
         <v>235</v>
       </c>
@@ -17844,7 +17877,7 @@
         <v>7538.5</v>
       </c>
     </row>
-    <row r="256" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A256" s="4" t="s">
         <v>235</v>
       </c>
@@ -17906,7 +17939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A257" s="4" t="s">
         <v>235</v>
       </c>
@@ -17968,7 +18001,7 @@
         <v>26675</v>
       </c>
     </row>
-    <row r="258" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A258" s="4" t="s">
         <v>235</v>
       </c>
@@ -18030,7 +18063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A259" s="4" t="s">
         <v>235</v>
       </c>
@@ -18092,7 +18125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A260" s="4" t="s">
         <v>235</v>
       </c>
@@ -18154,7 +18187,7 @@
         <v>1181986.0575000001</v>
       </c>
     </row>
-    <row r="261" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A261" s="4" t="s">
         <v>235</v>
       </c>
@@ -18216,7 +18249,7 @@
         <v>2625</v>
       </c>
     </row>
-    <row r="262" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A262" s="4" t="s">
         <v>235</v>
       </c>
@@ -18278,7 +18311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A263" s="4" t="s">
         <v>235</v>
       </c>
@@ -18340,7 +18373,7 @@
         <v>2430.0774999999999</v>
       </c>
     </row>
-    <row r="264" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A264" s="4" t="s">
         <v>235</v>
       </c>
@@ -18402,7 +18435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A265" s="4" t="s">
         <v>235</v>
       </c>
@@ -18464,7 +18497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A266" s="4" t="s">
         <v>235</v>
       </c>
@@ -18526,7 +18559,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="267" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A267" s="4" t="s">
         <v>235</v>
       </c>
@@ -18588,7 +18621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A268" s="4" t="s">
         <v>235</v>
       </c>
@@ -18650,7 +18683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A269" s="4" t="s">
         <v>235</v>
       </c>
@@ -18712,7 +18745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A270" s="4" t="s">
         <v>235</v>
       </c>
@@ -18774,7 +18807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A271" s="4" t="s">
         <v>235</v>
       </c>
@@ -18836,7 +18869,7 @@
         <v>582.9325</v>
       </c>
     </row>
-    <row r="272" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A272" s="4" t="s">
         <v>235</v>
       </c>
@@ -18898,7 +18931,7 @@
         <v>9795.4125000000004</v>
       </c>
     </row>
-    <row r="273" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A273" s="4" t="s">
         <v>235</v>
       </c>
@@ -18960,7 +18993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A274" s="4" t="s">
         <v>235</v>
       </c>
@@ -19022,7 +19055,7 @@
         <v>547.75</v>
       </c>
     </row>
-    <row r="275" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A275" s="4" t="s">
         <v>235</v>
       </c>
@@ -19084,7 +19117,7 @@
         <v>113222.7825</v>
       </c>
     </row>
-    <row r="276" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A276" s="4" t="s">
         <v>235</v>
       </c>
@@ -19146,7 +19179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A277" s="4" t="s">
         <v>394</v>
       </c>
@@ -19208,7 +19241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A278" s="4" t="s">
         <v>394</v>
       </c>
@@ -19270,7 +19303,7 @@
         <v>100275.26</v>
       </c>
     </row>
-    <row r="279" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A279" s="4" t="s">
         <v>394</v>
       </c>
@@ -19332,7 +19365,7 @@
         <v>406845.79249999998</v>
       </c>
     </row>
-    <row r="280" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A280" s="4" t="s">
         <v>394</v>
       </c>
@@ -19394,7 +19427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A281" s="4" t="s">
         <v>394</v>
       </c>
@@ -19456,7 +19489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A282" s="4" t="s">
         <v>394</v>
       </c>
@@ -19518,7 +19551,7 @@
         <v>527990</v>
       </c>
     </row>
-    <row r="283" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A283" s="4" t="s">
         <v>394</v>
       </c>
@@ -19580,7 +19613,7 @@
         <v>170125</v>
       </c>
     </row>
-    <row r="284" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A284" s="4" t="s">
         <v>394</v>
       </c>
@@ -19642,7 +19675,7 @@
         <v>666162.5</v>
       </c>
     </row>
-    <row r="285" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A285" s="4" t="s">
         <v>394</v>
       </c>
@@ -19704,7 +19737,7 @@
         <v>50250</v>
       </c>
     </row>
-    <row r="286" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A286" s="4" t="s">
         <v>394</v>
       </c>
@@ -19766,7 +19799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A287" s="4" t="s">
         <v>394</v>
       </c>
@@ -19828,7 +19861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A288" s="4" t="s">
         <v>394</v>
       </c>
@@ -19890,7 +19923,7 @@
         <v>3654.9074999999998</v>
       </c>
     </row>
-    <row r="289" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A289" s="4" t="s">
         <v>394</v>
       </c>
@@ -19952,7 +19985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A290" s="4" t="s">
         <v>394</v>
       </c>
@@ -20014,7 +20047,7 @@
         <v>2229138.5649999999</v>
       </c>
     </row>
-    <row r="291" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A291" s="4" t="s">
         <v>394</v>
       </c>
@@ -20076,7 +20109,7 @@
         <v>115997.8125</v>
       </c>
     </row>
-    <row r="292" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A292" s="4" t="s">
         <v>394</v>
       </c>
@@ -20138,7 +20171,7 @@
         <v>1410123.43</v>
       </c>
     </row>
-    <row r="293" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A293" s="4" t="s">
         <v>394</v>
       </c>
@@ -20200,7 +20233,7 @@
         <v>66175.442500000005</v>
       </c>
     </row>
-    <row r="294" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A294" s="4" t="s">
         <v>394</v>
       </c>
@@ -20262,7 +20295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A295" s="4" t="s">
         <v>394</v>
       </c>
@@ -20324,7 +20357,7 @@
         <v>32113.467499999999</v>
       </c>
     </row>
-    <row r="296" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A296" s="4" t="s">
         <v>394</v>
       </c>
@@ -20386,7 +20419,7 @@
         <v>217147.92249999999</v>
       </c>
     </row>
-    <row r="297" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A297" s="4" t="s">
         <v>394</v>
       </c>
@@ -20448,7 +20481,7 @@
         <v>437414.09749999997</v>
       </c>
     </row>
-    <row r="298" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A298" s="4" t="s">
         <v>394</v>
       </c>
@@ -20510,7 +20543,7 @@
         <v>2827295.8975</v>
       </c>
     </row>
-    <row r="299" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A299" s="4" t="s">
         <v>394</v>
       </c>
@@ -20572,7 +20605,7 @@
         <v>324258.88</v>
       </c>
     </row>
-    <row r="300" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A300" s="4" t="s">
         <v>394</v>
       </c>
@@ -20634,7 +20667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A301" s="4" t="s">
         <v>394</v>
       </c>
@@ -20696,7 +20729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A302" s="4" t="s">
         <v>394</v>
       </c>
@@ -20758,7 +20791,7 @@
         <v>98773.014999999999</v>
       </c>
     </row>
-    <row r="303" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A303" s="4" t="s">
         <v>394</v>
       </c>
@@ -20820,7 +20853,7 @@
         <v>5779433.7699999996</v>
       </c>
     </row>
-    <row r="304" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A304" s="4" t="s">
         <v>394</v>
       </c>
@@ -20882,7 +20915,7 @@
         <v>609984.91249999998</v>
       </c>
     </row>
-    <row r="305" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A305" s="4" t="s">
         <v>394</v>
       </c>
@@ -20944,7 +20977,7 @@
         <v>2158584.105</v>
       </c>
     </row>
-    <row r="306" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A306" s="4" t="s">
         <v>394</v>
       </c>
@@ -21006,7 +21039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A307" s="4" t="s">
         <v>394</v>
       </c>
@@ -21068,7 +21101,7 @@
         <v>307766.745</v>
       </c>
     </row>
-    <row r="308" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A308" s="4" t="s">
         <v>394</v>
       </c>
@@ -21130,7 +21163,7 @@
         <v>177692.065</v>
       </c>
     </row>
-    <row r="309" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A309" s="4" t="s">
         <v>394</v>
       </c>
@@ -21192,7 +21225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A310" s="4" t="s">
         <v>394</v>
       </c>
@@ -21254,7 +21287,7 @@
         <v>40546.980000000003</v>
       </c>
     </row>
-    <row r="311" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A311" s="4" t="s">
         <v>394</v>
       </c>
@@ -21316,7 +21349,7 @@
         <v>419871.51500000001</v>
       </c>
     </row>
-    <row r="312" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A312" s="4" t="s">
         <v>394</v>
       </c>
@@ -21378,7 +21411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A313" s="4" t="s">
         <v>394</v>
       </c>
@@ -21440,7 +21473,7 @@
         <v>878.77750000000003</v>
       </c>
     </row>
-    <row r="314" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A314" s="4" t="s">
         <v>394</v>
       </c>
@@ -21502,7 +21535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A315" s="4" t="s">
         <v>394</v>
       </c>
@@ -21564,7 +21597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A316" s="4" t="s">
         <v>394</v>
       </c>
@@ -21626,7 +21659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A317" s="4" t="s">
         <v>394</v>
       </c>
@@ -21688,7 +21721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A318" s="4" t="s">
         <v>394</v>
       </c>
@@ -21750,7 +21783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A319" s="4" t="s">
         <v>394</v>
       </c>
@@ -21812,7 +21845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A320" s="4" t="s">
         <v>394</v>
       </c>
@@ -21874,7 +21907,7 @@
         <v>17318.38</v>
       </c>
     </row>
-    <row r="321" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A321" s="4" t="s">
         <v>394</v>
       </c>
@@ -21936,7 +21969,7 @@
         <v>1735705.7749999999</v>
       </c>
     </row>
-    <row r="322" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A322" s="4" t="s">
         <v>394</v>
       </c>
@@ -21998,7 +22031,7 @@
         <v>8170229.8174999999</v>
       </c>
     </row>
-    <row r="323" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A323" s="4" t="s">
         <v>394</v>
       </c>
@@ -22060,7 +22093,7 @@
         <v>456081.495</v>
       </c>
     </row>
-    <row r="324" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A324" s="4" t="s">
         <v>394</v>
       </c>
@@ -22122,7 +22155,7 @@
         <v>18710057.317499999</v>
       </c>
     </row>
-    <row r="325" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A325" s="4" t="s">
         <v>394</v>
       </c>
@@ -22184,7 +22217,7 @@
         <v>1408048.69</v>
       </c>
     </row>
-    <row r="326" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A326" s="4" t="s">
         <v>394</v>
       </c>
@@ -22246,7 +22279,7 @@
         <v>5054932.8825000003</v>
       </c>
     </row>
-    <row r="327" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A327" s="4" t="s">
         <v>394</v>
       </c>
@@ -22308,7 +22341,7 @@
         <v>26882211.074999999</v>
       </c>
     </row>
-    <row r="328" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A328" s="4" t="s">
         <v>394</v>
       </c>
@@ -22370,7 +22403,7 @@
         <v>1859621.8875</v>
       </c>
     </row>
-    <row r="329" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A329" s="4" t="s">
         <v>394</v>
       </c>
@@ -22432,7 +22465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A330" s="4" t="s">
         <v>394</v>
       </c>
@@ -22494,7 +22527,7 @@
         <v>2283328.0350000001</v>
       </c>
     </row>
-    <row r="331" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A331" s="4" t="s">
         <v>394</v>
       </c>
@@ -22556,7 +22589,7 @@
         <v>19620496.107500002</v>
       </c>
     </row>
-    <row r="332" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A332" s="4" t="s">
         <v>394</v>
       </c>
@@ -22618,7 +22651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A333" s="4" t="s">
         <v>394</v>
       </c>
@@ -22680,7 +22713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A334" s="4" t="s">
         <v>394</v>
       </c>
@@ -22742,7 +22775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A335" s="4" t="s">
         <v>394</v>
       </c>
@@ -22804,7 +22837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A336" s="4" t="s">
         <v>394</v>
       </c>
@@ -22866,7 +22899,7 @@
         <v>3225617.6274999999</v>
       </c>
     </row>
-    <row r="337" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A337" s="4" t="s">
         <v>394</v>
       </c>
@@ -22928,7 +22961,7 @@
         <v>7989959.9874999998</v>
       </c>
     </row>
-    <row r="338" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A338" s="4" t="s">
         <v>394</v>
       </c>
@@ -22990,7 +23023,7 @@
         <v>538806.27749999997</v>
       </c>
     </row>
-    <row r="339" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A339" s="4" t="s">
         <v>394</v>
       </c>
@@ -23052,7 +23085,7 @@
         <v>1186322.5774999999</v>
       </c>
     </row>
-    <row r="340" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A340" s="4" t="s">
         <v>394</v>
       </c>
@@ -23114,7 +23147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A341" s="4" t="s">
         <v>394</v>
       </c>
@@ -23176,7 +23209,7 @@
         <v>6380939.7050000001</v>
       </c>
     </row>
-    <row r="342" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A342" s="4" t="s">
         <v>394</v>
       </c>
@@ -23238,7 +23271,7 @@
         <v>277041.33500000002</v>
       </c>
     </row>
-    <row r="343" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A343" s="4" t="s">
         <v>394</v>
       </c>
@@ -23300,7 +23333,7 @@
         <v>214916.64749999999</v>
       </c>
     </row>
-    <row r="344" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A344" s="4" t="s">
         <v>394</v>
       </c>
@@ -23362,7 +23395,7 @@
         <v>449848.9</v>
       </c>
     </row>
-    <row r="345" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A345" s="4" t="s">
         <v>394</v>
       </c>
@@ -23424,7 +23457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A346" s="4" t="s">
         <v>394</v>
       </c>
@@ -23486,7 +23519,7 @@
         <v>11988232.7775</v>
       </c>
     </row>
-    <row r="347" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A347" s="4" t="s">
         <v>394</v>
       </c>
@@ -23548,7 +23581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A348" s="4" t="s">
         <v>394</v>
       </c>
@@ -23610,7 +23643,7 @@
         <v>72513433.417500004</v>
       </c>
     </row>
-    <row r="349" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A349" s="4" t="s">
         <v>394</v>
       </c>
@@ -23672,7 +23705,7 @@
         <v>45476.26</v>
       </c>
     </row>
-    <row r="350" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A350" s="4" t="s">
         <v>394</v>
       </c>
@@ -23734,7 +23767,7 @@
         <v>40321.042500000003</v>
       </c>
     </row>
-    <row r="351" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A351" s="4" t="s">
         <v>394</v>
       </c>
@@ -23796,7 +23829,7 @@
         <v>134310</v>
       </c>
     </row>
-    <row r="352" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A352" s="4" t="s">
         <v>394</v>
       </c>
@@ -23858,7 +23891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A353" s="4" t="s">
         <v>394</v>
       </c>
@@ -23920,7 +23953,7 @@
         <v>3651913.4950000001</v>
       </c>
     </row>
-    <row r="354" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A354" s="4" t="s">
         <v>394</v>
       </c>
@@ -23982,7 +24015,7 @@
         <v>18753669.602499999</v>
       </c>
     </row>
-    <row r="355" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A355" s="4" t="s">
         <v>394</v>
       </c>
@@ -24044,7 +24077,7 @@
         <v>130108401.4425</v>
       </c>
     </row>
-    <row r="356" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A356" s="4" t="s">
         <v>394</v>
       </c>
@@ -24106,7 +24139,7 @@
         <v>1398860.41</v>
       </c>
     </row>
-    <row r="357" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A357" s="4" t="s">
         <v>394</v>
       </c>
@@ -24168,7 +24201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A358" s="4" t="s">
         <v>394</v>
       </c>
@@ -24230,7 +24263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A359" s="4" t="s">
         <v>394</v>
       </c>
@@ -24292,7 +24325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A360" s="4" t="s">
         <v>394</v>
       </c>
@@ -24354,7 +24387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A361" s="4" t="s">
         <v>394</v>
       </c>
@@ -24416,7 +24449,7 @@
         <v>13711808.52</v>
       </c>
     </row>
-    <row r="362" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A362" s="4" t="s">
         <v>394</v>
       </c>
@@ -24478,7 +24511,7 @@
         <v>8673289.0625</v>
       </c>
     </row>
-    <row r="363" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A363" s="4" t="s">
         <v>394</v>
       </c>
@@ -24540,7 +24573,7 @@
         <v>32344617.682500001</v>
       </c>
     </row>
-    <row r="364" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A364" s="4" t="s">
         <v>394</v>
       </c>
@@ -24602,7 +24635,7 @@
         <v>960799.80500000005</v>
       </c>
     </row>
-    <row r="365" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A365" s="4" t="s">
         <v>394</v>
       </c>
@@ -24664,7 +24697,7 @@
         <v>219292.41250000001</v>
       </c>
     </row>
-    <row r="366" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A366" s="4" t="s">
         <v>394</v>
       </c>
@@ -24726,7 +24759,7 @@
         <v>307252.70750000002</v>
       </c>
     </row>
-    <row r="367" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A367" s="4" t="s">
         <v>394</v>
       </c>
@@ -24788,7 +24821,7 @@
         <v>438852.125</v>
       </c>
     </row>
-    <row r="368" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A368" s="4" t="s">
         <v>394</v>
       </c>
@@ -24850,7 +24883,7 @@
         <v>2063512.8875</v>
       </c>
     </row>
-    <row r="369" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A369" s="4" t="s">
         <v>394</v>
       </c>
@@ -24912,7 +24945,7 @@
         <v>915333.98499999999</v>
       </c>
     </row>
-    <row r="370" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A370" s="4" t="s">
         <v>394</v>
       </c>
@@ -24974,7 +25007,7 @@
         <v>2179391.1575000002</v>
       </c>
     </row>
-    <row r="371" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A371" s="4" t="s">
         <v>394</v>
       </c>
@@ -25036,7 +25069,7 @@
         <v>72790922.702500001</v>
       </c>
     </row>
-    <row r="372" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A372" s="4" t="s">
         <v>394</v>
       </c>
@@ -25098,7 +25131,7 @@
         <v>47631.197500000002</v>
       </c>
     </row>
-    <row r="373" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A373" s="4" t="s">
         <v>394</v>
       </c>
@@ -25160,7 +25193,7 @@
         <v>3070640.8525</v>
       </c>
     </row>
-    <row r="374" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A374" s="4" t="s">
         <v>394</v>
       </c>
@@ -25222,7 +25255,7 @@
         <v>11491011.74</v>
       </c>
     </row>
-    <row r="375" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A375" s="4" t="s">
         <v>394</v>
       </c>
@@ -25284,7 +25317,7 @@
         <v>593216.08499999996</v>
       </c>
     </row>
-    <row r="376" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A376" s="4" t="s">
         <v>394</v>
       </c>
@@ -25346,7 +25379,7 @@
         <v>210728689.73500001</v>
       </c>
     </row>
-    <row r="377" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A377" s="4" t="s">
         <v>394</v>
       </c>
@@ -25408,7 +25441,7 @@
         <v>5268395.6924999999</v>
       </c>
     </row>
-    <row r="378" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A378" s="4" t="s">
         <v>394</v>
       </c>
@@ -25470,7 +25503,7 @@
         <v>64432147.560000002</v>
       </c>
     </row>
-    <row r="379" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A379" s="4" t="s">
         <v>394</v>
       </c>
@@ -25532,7 +25565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A380" s="4" t="s">
         <v>394</v>
       </c>
@@ -25594,7 +25627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A381" s="4" t="s">
         <v>394</v>
       </c>
@@ -25656,7 +25689,7 @@
         <v>4965675.97</v>
       </c>
     </row>
-    <row r="382" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A382" s="4" t="s">
         <v>394</v>
       </c>
@@ -25718,7 +25751,7 @@
         <v>30253.794999999998</v>
       </c>
     </row>
-    <row r="383" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A383" s="4" t="s">
         <v>394</v>
       </c>
@@ -25780,7 +25813,7 @@
         <v>314473.64250000002</v>
       </c>
     </row>
-    <row r="384" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A384" s="4" t="s">
         <v>394</v>
       </c>
@@ -25842,7 +25875,7 @@
         <v>1486251.5</v>
       </c>
     </row>
-    <row r="385" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A385" s="4" t="s">
         <v>394</v>
       </c>
@@ -25904,7 +25937,7 @@
         <v>2390782.9049999998</v>
       </c>
     </row>
-    <row r="386" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A386" s="4" t="s">
         <v>394</v>
       </c>
@@ -25966,7 +25999,7 @@
         <v>1584279.57</v>
       </c>
     </row>
-    <row r="387" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A387" s="4" t="s">
         <v>394</v>
       </c>
@@ -26028,7 +26061,7 @@
         <v>499758.90250000003</v>
       </c>
     </row>
-    <row r="388" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A388" s="4" t="s">
         <v>394</v>
       </c>
@@ -26090,23 +26123,11 @@
         <v>324569.46500000003</v>
       </c>
     </row>
-    <row r="389" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="Q389" s="7">
-        <f>SUM(Q3:Q388)</f>
-        <v>3178156131</v>
-      </c>
-      <c r="R389" s="7">
-        <f t="shared" ref="R389:T389" si="0">SUM(R3:R388)</f>
-        <v>2933215209.3560004</v>
-      </c>
-      <c r="S389" s="7">
-        <f t="shared" si="0"/>
-        <v>2741860412.6085019</v>
-      </c>
-      <c r="T389" s="7">
-        <f t="shared" si="0"/>
-        <v>2500245254.2850013</v>
-      </c>
+    <row r="389" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Q389" s="8"/>
+      <c r="R389" s="8"/>
+      <c r="S389" s="8"/>
+      <c r="T389" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">
